--- a/output/pdf_financials_xlsx/WVM.xlsx
+++ b/output/pdf_financials_xlsx/WVM.xlsx
@@ -1301,34 +1301,34 @@
         <v>7.290914</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.139276</v>
+        <v>-1.139276</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.097415</v>
+        <v>-1.097415</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.029562</v>
+        <v>-1.029562</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.77034</v>
+        <v>-0.77034</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.489633</v>
+        <v>-1.489633</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.886403</v>
+        <v>-1.886403</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.821805</v>
+        <v>-1.821805</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.683073</v>
+        <v>-1.683073</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2.576125</v>
+        <v>-2.576125</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>2.256733</v>
+        <v>-2.256733</v>
       </c>
     </row>
     <row r="17">
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.145795</v>
+        <v>-8.403489</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.017702</v>
+        <v>-8.353782000000001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.127273</v>
+        <v>-14.581869</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-14.581828</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1581,46 +1581,46 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.274642</v>
+        <v>-4.274642</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.16804</v>
+        <v>-4.16804</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7.227298</v>
+        <v>-7.227298</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.290914</v>
+        <v>-7.290914</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.139276</v>
+        <v>-1.139276</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.097415</v>
+        <v>-1.097415</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.029562</v>
+        <v>-1.029562</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.77034</v>
+        <v>-0.77034</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.489633</v>
+        <v>-1.489633</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.886403</v>
+        <v>-1.886403</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.821805</v>
+        <v>-1.821805</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.683073</v>
+        <v>-1.683073</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>2.576125</v>
+        <v>-2.576125</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.256733</v>
+        <v>-2.256733</v>
       </c>
     </row>
     <row r="21">
@@ -1754,46 +1754,46 @@
         <v>-0.040698</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.274642</v>
+        <v>-4.274642</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.16804</v>
+        <v>-4.16804</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.227298</v>
+        <v>-7.227298</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.290914</v>
+        <v>-7.290914</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.139276</v>
+        <v>-1.139276</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.097415</v>
+        <v>-1.097415</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.029562</v>
+        <v>-1.029562</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.77034</v>
+        <v>-0.77034</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.489633</v>
+        <v>-1.489633</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.886403</v>
+        <v>-1.886403</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.821805</v>
+        <v>-1.821805</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.683073</v>
+        <v>-1.683073</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>2.576125</v>
+        <v>-2.576125</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2.256733</v>
+        <v>-2.256733</v>
       </c>
     </row>
     <row r="24">
@@ -1931,16 +1931,16 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>26.716512</v>
+        <v>-26.716512</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>34.733667</v>
+        <v>-34.733667</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>60.227483</v>
+        <v>-60.227483</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>243.030467</v>
+        <v>-243.030467</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>62.8801</v>
+        <v>-62.8801</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>60.726833</v>
+        <v>-60.726833</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>56.102433</v>
+        <v>-56.102433</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>64.403125</v>
+        <v>-64.403125</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>56.418325</v>
+        <v>-56.418325</v>
       </c>
     </row>
     <row r="27">
@@ -2012,34 +2012,34 @@
         <v>7.290914</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.139276</v>
+        <v>-1.139276</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.097415</v>
+        <v>-1.097415</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.029562</v>
+        <v>-1.029562</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.77034</v>
+        <v>-0.77034</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.489633</v>
+        <v>-1.489633</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.886403</v>
+        <v>-1.886403</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.821805</v>
+        <v>-1.821805</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.683073</v>
+        <v>-1.683073</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.576125</v>
+        <v>-2.576125</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.256733</v>
+        <v>-2.256733</v>
       </c>
     </row>
     <row r="28">
@@ -2130,34 +2130,34 @@
         <v>7.301997</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.147654</v>
+        <v>-1.130898</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.106384</v>
+        <v>-1.088446</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.037498</v>
+        <v>-1.021626</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.791071</v>
+        <v>-0.749609</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.489633</v>
+        <v>-1.489633</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.886403</v>
+        <v>-1.886403</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.821805</v>
+        <v>-1.821805</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.686427</v>
+        <v>-1.679719</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.579529</v>
+        <v>-2.572721</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.260207</v>
+        <v>-2.253259</v>
       </c>
     </row>
     <row r="30">
@@ -2264,46 +2264,46 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.53113108817062</v>
+        <v>203.5311310881706</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.4229118756005506</v>
+        <v>199.5770881243994</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.730529217815696</v>
+        <v>198.2694707821843</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5848,46 +5848,46 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.055591</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.191566</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.382503</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>2.275526</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>8.522097</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>7.340613</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>4.691403</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>8.122346</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>6.034285</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>4.807721</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>7.81611</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>6.687342</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>10.851048</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>8.389884</v>
       </c>
     </row>
     <row r="92">
@@ -5903,46 +5903,46 @@
         <v>0.002096</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.098495</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.082606</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.96498</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.590738</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.207906</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.301687</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.493327</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.604662</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.707874</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.427226</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.449847</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.36784</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.452471</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.792144</v>
       </c>
     </row>
     <row r="93">
@@ -9868,7 +9868,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -9958,7 +9962,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11124,7 +11132,11 @@
           <t>Warrant reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11218,7 +11230,11 @@
           <t>Share based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12514,7 +12530,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -12600,7 +12620,11 @@
           <t>Share based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -12968,7 +12992,11 @@
           <t>Warrant reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13058,7 +13086,11 @@
           <t>Share based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -32620,10 +32652,10 @@
         </is>
       </c>
       <c r="S262" s="5" t="n">
-        <v>2.576125</v>
+        <v>-2.576125</v>
       </c>
       <c r="T262" s="5" t="n">
-        <v>2.256733</v>
+        <v>-2.256733</v>
       </c>
     </row>
     <row r="263">
@@ -33677,34 +33709,34 @@
         </is>
       </c>
       <c r="J274" s="5" t="n">
-        <v>7.290914</v>
+        <v>-7.290914</v>
       </c>
       <c r="K274" s="5" t="n">
-        <v>1.139276</v>
+        <v>-1.139276</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>1.097415</v>
+        <v>-1.097415</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>1.029562</v>
+        <v>-1.029562</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>0.77034</v>
+        <v>-0.77034</v>
       </c>
       <c r="O274" s="5" t="n">
-        <v>1.489633</v>
+        <v>-1.489633</v>
       </c>
       <c r="P274" s="5" t="n">
-        <v>1.886403</v>
+        <v>-1.886403</v>
       </c>
       <c r="Q274" s="5" t="n">
-        <v>1.821805</v>
+        <v>-1.821805</v>
       </c>
       <c r="R274" s="5" t="n">
-        <v>1.683073</v>
+        <v>-1.683073</v>
       </c>
       <c r="S274" s="5" t="n">
-        <v>2.576125</v>
+        <v>-2.576125</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -36701,16 +36733,16 @@
         </is>
       </c>
       <c r="L306" s="5" t="n">
-        <v>1.097415</v>
+        <v>-1.097415</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>1.029562</v>
+        <v>-1.029562</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>0.77034</v>
+        <v>-0.77034</v>
       </c>
       <c r="O306" s="5" t="n">
-        <v>1.489633</v>
+        <v>-1.489633</v>
       </c>
       <c r="P306" t="inlineStr">
         <is>
@@ -38117,10 +38149,10 @@
         </is>
       </c>
       <c r="L321" s="5" t="n">
-        <v>2.278899</v>
+        <v>-2.278899</v>
       </c>
       <c r="M321" s="5" t="n">
-        <v>3.701929</v>
+        <v>-3.701929</v>
       </c>
       <c r="N321" t="inlineStr">
         <is>
@@ -39884,16 +39916,16 @@
         </is>
       </c>
       <c r="G340" s="5" t="n">
-        <v>4.274642</v>
+        <v>-4.274642</v>
       </c>
       <c r="H340" s="5" t="n">
-        <v>4.16804</v>
+        <v>-4.16804</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>7.227298</v>
+        <v>-7.227298</v>
       </c>
       <c r="J340" s="5" t="n">
-        <v>7.290914</v>
+        <v>-7.290914</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
@@ -39988,10 +40020,10 @@
         </is>
       </c>
       <c r="I341" s="5" t="n">
-        <v>6.653229</v>
+        <v>-6.653229</v>
       </c>
       <c r="J341" s="5" t="n">
-        <v>5.397891</v>
+        <v>-5.397891</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
@@ -40650,10 +40682,10 @@
         </is>
       </c>
       <c r="G348" s="5" t="n">
-        <v>4.285387</v>
+        <v>-4.285387</v>
       </c>
       <c r="H348" s="5" t="n">
-        <v>4.304015</v>
+        <v>-4.304015</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WVM.xlsx
+++ b/output/pdf_financials_xlsx/WVM.xlsx
@@ -1056,43 +1056,43 @@
         <v>-0.032677</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.513159</v>
+        <v>-0.009159</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004985</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.044677</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012678</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002619</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004958</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004412</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016899</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006074</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.123376</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.245775</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.213539</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.12218</v>
       </c>
     </row>
     <row r="13">
@@ -2003,43 +2003,43 @@
         <v>4.161524</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.698901</v>
+        <v>4.194901</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.354571</v>
+        <v>7.359556</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7.290914</v>
+        <v>7.335591</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.139276</v>
+        <v>-1.126598</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.097415</v>
+        <v>-1.094796</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.029562</v>
+        <v>-1.024604</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.77034</v>
+        <v>-0.7659280000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.489633</v>
+        <v>-1.472734</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.886403</v>
+        <v>-1.880329</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.821805</v>
+        <v>-1.698429</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.683073</v>
+        <v>-1.437298</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.576125</v>
+        <v>-2.362586</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.256733</v>
+        <v>-2.134553</v>
       </c>
     </row>
     <row r="28">
@@ -2121,43 +2121,43 @@
         <v>4.211002</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.744979</v>
+        <v>4.240979</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.363753</v>
+        <v>7.368738</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.301997</v>
+        <v>7.346674</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.130898</v>
+        <v>-1.11822</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.088446</v>
+        <v>-1.085827</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.021626</v>
+        <v>-1.016668</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.749609</v>
+        <v>-0.745197</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.489633</v>
+        <v>-1.472734</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.886403</v>
+        <v>-1.880329</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.821805</v>
+        <v>-1.698429</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.679719</v>
+        <v>-1.433944</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.572721</v>
+        <v>-2.359182</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.253259</v>
+        <v>-2.131079</v>
       </c>
     </row>
     <row r="30">
@@ -2406,57 +2406,53 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.334211</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.322168</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.655863</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.174184</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.565397</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.391908</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.155385</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.021407</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.228492</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.5054</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.051642</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>7.145088</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>6.326323</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.547091</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.541775</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.758253</v>
       </c>
     </row>
     <row r="35">
@@ -2524,57 +2520,53 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.334211</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.322168</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.655863</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.174184</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.565397</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.391908</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.155385</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.021407</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.228492</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.5054</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.051642</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>7.145088</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>6.326323</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>4.035201</v>
+        <v>4.582292</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>3.270519</v>
+        <v>3.812294</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.725104</v>
+        <v>2.483357</v>
       </c>
     </row>
     <row r="37">
@@ -3243,46 +3235,46 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.725016</v>
+        <v>0.06915300000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.209335</v>
+        <v>0.035151</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.584665</v>
+        <v>0.019268</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.498783</v>
+        <v>0.106875</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.196838</v>
+        <v>0.041453</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.056242</v>
+        <v>0.034835</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.265108</v>
+        <v>0.036616</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.530384</v>
+        <v>0.024984</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.07556599999999999</v>
+        <v>0.023924</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>7.21021</v>
+        <v>0.065122</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.392241</v>
+        <v>0.065918</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.634947</v>
+        <v>0.087856</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.618194</v>
+        <v>0.076419</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.835255</v>
+        <v>0.077002</v>
       </c>
     </row>
     <row r="49">
@@ -8472,7 +8464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13374,7 +13366,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -14778,7 +14770,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -17436,7 +17428,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -32480,7 +32472,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -33600,7 +33592,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -40282,7 +40274,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">

--- a/output/pdf_financials_xlsx/WVM.xlsx
+++ b/output/pdf_financials_xlsx/WVM.xlsx
@@ -6346,13 +6346,13 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.003354</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.003404</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.003474</v>
       </c>
     </row>
     <row r="101">
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.016402</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -29148,7 +29148,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -32186,7 +32190,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -34520,7 +34524,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">

--- a/output/pdf_financials_xlsx/WVM.xlsx
+++ b/output/pdf_financials_xlsx/WVM.xlsx
@@ -6698,28 +6698,28 @@
         <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.157844</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.012759</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.073933</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.56042</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.002598</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.248072</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.239971</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.209307</v>
       </c>
       <c r="L107" s="3" t="n">
         <v>0</v>
@@ -6731,13 +6731,13 @@
         <v>0</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.224545</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.101978</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.676995</v>
       </c>
     </row>
     <row r="108">
@@ -6890,19 +6890,19 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.679209</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.929692</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>1.069759</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>1.204277</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>1.36312</v>
       </c>
     </row>
     <row r="111">
@@ -7174,10 +7174,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>9.217425</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>6.65715</v>
       </c>
     </row>
     <row r="116">
@@ -7502,10 +7502,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.272736</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-0.311677</v>
       </c>
       <c r="P121" s="3" t="n">
         <v>0</v>
@@ -19118,7 +19118,11 @@
           <t>Accretion (Note 7)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -19680,7 +19684,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -20254,7 +20262,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -21578,7 +21590,11 @@
           <t>Proceeds from short term investments</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -21958,7 +21974,11 @@
           <t>Repurchase common shares $</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -22892,7 +22912,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -23832,7 +23856,11 @@
           <t>Repurchase shares $</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -28672,7 +28700,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -29624,7 +29656,11 @@
           <t>Share based compensation expense</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
